--- a/docs/sample-output/13-data-center/proforma.xlsx
+++ b/docs/sample-output/13-data-center/proforma.xlsx
@@ -264,7 +264,7 @@
     <t>Leverage Impact</t>
   </si>
   <si>
-    <t>Optimal holding period: Year 1 at 35.40% equity IRR. Leverage is positive when the equity IRR exceeds the property IRR.</t>
+    <t>Optimal holding period: Year 1 at 35.55% equity IRR. Leverage is positive when the equity IRR exceeds the property IRR.</t>
   </si>
   <si>
     <t>Acquisition-Price Sensitivity   ·   Ashburn Campus — 24 MW data center · 5-Year Before-Tax</t>
@@ -1046,7 +1046,7 @@
         <v>18</v>
       </c>
       <c r="B13" s="6">
-        <v>493856921.96</v>
+        <v>493631982.91</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -1054,7 +1054,7 @@
         <v>19</v>
       </c>
       <c r="B14" s="7">
-        <v>0.06786580993333659</v>
+        <v>0.0678967351394464</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -1062,7 +1062,7 @@
         <v>20</v>
       </c>
       <c r="B15" s="6">
-        <v>176059992.67873996</v>
+        <v>175979801.90741497</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -1078,7 +1078,7 @@
         <v>22</v>
       </c>
       <c r="B17" s="7">
-        <v>0.17219459294730124</v>
+        <v>0.1724491279226308</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -1086,7 +1086,7 @@
         <v>23</v>
       </c>
       <c r="B18" s="8">
-        <v>2.115039720503993</v>
+        <v>2.1170925204649955</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -1102,7 +1102,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="7">
-        <v>0.3540253766423883</v>
+        <v>0.3555268178087002</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -1117,7 +1117,7 @@
         <v>27</v>
       </c>
       <c r="B22" s="6">
-        <v>493856921.96</v>
+        <v>493631982.91</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -1133,7 +1133,7 @@
         <v>29</v>
       </c>
       <c r="B24" s="6">
-        <v>3210069.99274</v>
+        <v>3208607.8889150005</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -1141,7 +1141,7 @@
         <v>30</v>
       </c>
       <c r="B25" s="6">
-        <v>493856921.96</v>
+        <v>493631982.91</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -1149,7 +1149,7 @@
         <v>31</v>
       </c>
       <c r="B26" s="6">
-        <v>-321006999.274</v>
+        <v>-320860788.89150006</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -1157,7 +1157,7 @@
         <v>32</v>
       </c>
       <c r="B27" s="10">
-        <v>176059992.67873996</v>
+        <v>175979801.90741497</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -1165,7 +1165,7 @@
         <v>33</v>
       </c>
       <c r="B28" s="11">
-        <v>9.7987484515873</v>
+        <v>9.794285375198413</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -1173,7 +1173,7 @@
         <v>34</v>
       </c>
       <c r="B29" s="12">
-        <v>1714.7809790277777</v>
+        <v>1713.9999406597224</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -1188,7 +1188,7 @@
         <v>36</v>
       </c>
       <c r="B31" s="6">
-        <v>321006999.274</v>
+        <v>320860788.89150006</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -1220,7 +1220,7 @@
         <v>42</v>
       </c>
       <c r="B35" s="12">
-        <v>2167462.2475252203</v>
+        <v>2166475.0245519467</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -1228,7 +1228,7 @@
         <v>43</v>
       </c>
       <c r="B36" s="6">
-        <v>26009546.97030264</v>
+        <v>25997700.29462336</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -1236,7 +1236,7 @@
         <v>44</v>
       </c>
       <c r="B37" s="7">
-        <v>0.65</v>
+        <v>0.6500000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1463,19 +1463,19 @@
         <v>60</v>
       </c>
       <c r="B13" s="16">
-        <v>-26009546.97030264</v>
+        <v>-25997700.29462336</v>
       </c>
       <c r="C13" s="16">
-        <v>-26009546.97030264</v>
+        <v>-25997700.29462336</v>
       </c>
       <c r="D13" s="16">
-        <v>-26009546.97030264</v>
+        <v>-25997700.29462336</v>
       </c>
       <c r="E13" s="16">
-        <v>-26009546.97030264</v>
+        <v>-25997700.29462336</v>
       </c>
       <c r="F13" s="16">
-        <v>-26009546.97030264</v>
+        <v>-25997700.29462336</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1483,19 +1483,19 @@
         <v>61</v>
       </c>
       <c r="B14" s="18">
-        <v>7506453.029697359</v>
+        <v>7518299.70537664</v>
       </c>
       <c r="C14" s="18">
-        <v>8511933.029697359</v>
+        <v>8523779.70537664</v>
       </c>
       <c r="D14" s="18">
-        <v>9547577.429697357</v>
+        <v>9559424.105376638</v>
       </c>
       <c r="E14" s="18">
-        <v>10614291.161697358</v>
+        <v>10626137.83737664</v>
       </c>
       <c r="F14" s="18">
-        <v>11713006.305657357</v>
+        <v>11724852.981336638</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1639,19 +1639,19 @@
         <v>68</v>
       </c>
       <c r="B9" s="16">
-        <v>-315706855.1311849</v>
+        <v>-315563058.82720715</v>
       </c>
       <c r="C9" s="16">
-        <v>-310051750.519245</v>
+        <v>-309910529.96909904</v>
       </c>
       <c r="D9" s="16">
-        <v>-304017913.0781754</v>
+        <v>-303879440.78486556</v>
       </c>
       <c r="E9" s="16">
-        <v>-297579978.36899513</v>
+        <v>-297444438.38837147</v>
       </c>
       <c r="F9" s="16">
-        <v>-290710883.24926955</v>
+        <v>-290578471.9637434</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1659,19 +1659,19 @@
         <v>69</v>
       </c>
       <c r="B10" s="18">
-        <v>230883244.86881512</v>
+        <v>231027041.17279285</v>
       </c>
       <c r="C10" s="18">
-        <v>252936299.48075497</v>
+        <v>253077520.03090096</v>
       </c>
       <c r="D10" s="18">
-        <v>275859236.9218246</v>
+        <v>275997709.21513444</v>
       </c>
       <c r="E10" s="18">
-        <v>299693571.63100487</v>
+        <v>299829111.61162853</v>
       </c>
       <c r="F10" s="18">
-        <v>324480616.75073045</v>
+        <v>324613028.0362566</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1709,19 +1709,19 @@
         <v>71</v>
       </c>
       <c r="B13" s="21">
-        <v>0.5487137662658464</v>
+        <v>0.5484638413426199</v>
       </c>
       <c r="C13" s="21">
-        <v>0.5231890143907721</v>
+        <v>0.5229507153316026</v>
       </c>
       <c r="D13" s="21">
-        <v>0.49806587037317585</v>
+        <v>0.49783901425607524</v>
       </c>
       <c r="E13" s="21">
-        <v>0.47331910052026477</v>
+        <v>0.47310351591653926</v>
       </c>
       <c r="F13" s="21">
-        <v>0.4489258045450987</v>
+        <v>0.4487213304565428</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1729,19 +1729,19 @@
         <v>72</v>
       </c>
       <c r="B14" s="22">
-        <v>1.2886037591607469</v>
+        <v>1.2891909522832492</v>
       </c>
       <c r="C14" s="22">
-        <v>1.3272618719355693</v>
+        <v>1.3278666808517468</v>
       </c>
       <c r="D14" s="22">
-        <v>1.3670797280936364</v>
+        <v>1.3677026812772992</v>
       </c>
       <c r="E14" s="22">
-        <v>1.4080921199364456</v>
+        <v>1.4087337617156181</v>
       </c>
       <c r="F14" s="22">
-        <v>1.4503348835345389</v>
+        <v>1.4509957745670867</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1749,19 +1749,19 @@
         <v>73</v>
       </c>
       <c r="B15" s="21">
-        <v>0.10440893835897937</v>
+        <v>0.10445651559914829</v>
       </c>
       <c r="C15" s="21">
-        <v>0.10754120650974874</v>
+        <v>0.10759021106712273</v>
       </c>
       <c r="D15" s="21">
-        <v>0.11076744270504121</v>
+        <v>0.1108179173991364</v>
       </c>
       <c r="E15" s="21">
-        <v>0.11409046598619245</v>
+        <v>0.1141424549211105</v>
       </c>
       <c r="F15" s="21">
-        <v>0.11751317996577822</v>
+        <v>0.11756672856874381</v>
       </c>
     </row>
   </sheetData>
@@ -1837,19 +1837,19 @@
         <v>75</v>
       </c>
       <c r="B5" s="21">
-        <v>0.04263576815770138</v>
+        <v>0.042722514878906985</v>
       </c>
       <c r="C5" s="21">
-        <v>0.048346776006229</v>
+        <v>0.04843612512907078</v>
       </c>
       <c r="D5" s="21">
-        <v>0.054229114090212444</v>
+        <v>0.05432114368673947</v>
       </c>
       <c r="E5" s="21">
-        <v>0.060287922316715405</v>
+        <v>0.06038271280113825</v>
       </c>
       <c r="F5" s="21">
-        <v>0.06652849479001345</v>
+        <v>0.06662612898896897</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1857,19 +1857,19 @@
         <v>76</v>
       </c>
       <c r="B6" s="21">
-        <v>0.03251190026353982</v>
+        <v>0.0325429424504184</v>
       </c>
       <c r="C6" s="21">
-        <v>0.03365247711447997</v>
+        <v>0.033680509056418284</v>
       </c>
       <c r="D6" s="21">
-        <v>0.034610323497715735</v>
+        <v>0.034635882060619815</v>
       </c>
       <c r="E6" s="21">
-        <v>0.03541714660054875</v>
+        <v>0.03544064744166929</v>
       </c>
       <c r="F6" s="21">
-        <v>0.03609770723117004</v>
+        <v>0.03611947755845175</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1877,19 +1877,19 @@
         <v>77</v>
       </c>
       <c r="B7" s="23">
-        <v>1.354025376642533</v>
+        <v>1.3555268178087334</v>
       </c>
       <c r="C7" s="23">
-        <v>1.5276309026714345</v>
+        <v>1.5292641344331162</v>
       </c>
       <c r="D7" s="23">
-        <v>1.712059598689936</v>
+        <v>1.713828572724154</v>
       </c>
       <c r="E7" s="23">
-        <v>1.9077237319591946</v>
+        <v>1.9096325221569375</v>
       </c>
       <c r="F7" s="23">
-        <v>2.115039720503993</v>
+        <v>2.1170925204649955</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1897,19 +1897,19 @@
         <v>78</v>
       </c>
       <c r="B8" s="21">
-        <v>0.1746440602629551</v>
+        <v>0.17517932403838643</v>
       </c>
       <c r="C8" s="21">
-        <v>0.13440340627744574</v>
+        <v>0.13466981089339997</v>
       </c>
       <c r="D8" s="21">
-        <v>0.12131773124636173</v>
+        <v>0.12149868331542588</v>
       </c>
       <c r="E8" s="21">
-        <v>0.11484476769496266</v>
+        <v>0.11498381670521263</v>
       </c>
       <c r="F8" s="21">
-        <v>0.11098881746494318</v>
+        <v>0.11110302507911413</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1937,19 +1937,19 @@
         <v>80</v>
       </c>
       <c r="B10" s="24">
-        <v>0.3540253766423883</v>
+        <v>0.3555268178087002</v>
       </c>
       <c r="C10" s="24">
-        <v>0.24010809846994857</v>
+        <v>0.24078650027891144</v>
       </c>
       <c r="D10" s="24">
-        <v>0.2029877504732667</v>
+        <v>0.2034233325881487</v>
       </c>
       <c r="E10" s="24">
-        <v>0.1840097054908012</v>
+        <v>0.18433050267512574</v>
       </c>
       <c r="F10" s="24">
-        <v>0.17219459294730124</v>
+        <v>0.1724491279226308</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1957,19 +1957,19 @@
         <v>81</v>
       </c>
       <c r="B11" s="21">
-        <v>0.17939999999999998</v>
+        <v>0.1803</v>
       </c>
       <c r="C11" s="21">
-        <v>0.10570000000000002</v>
+        <v>0.1061</v>
       </c>
       <c r="D11" s="21">
-        <v>0.08170000000000001</v>
+        <v>0.0819</v>
       </c>
       <c r="E11" s="21">
-        <v>0.0692</v>
+        <v>0.06929999999999999</v>
       </c>
       <c r="F11" s="21">
-        <v>0.06119999999999999</v>
+        <v>0.06129999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2063,19 +2063,19 @@
         <v>18</v>
       </c>
       <c r="B6" s="18">
-        <v>444471230</v>
+        <v>444268785</v>
       </c>
       <c r="C6" s="18">
-        <v>469164076</v>
+        <v>468950384</v>
       </c>
       <c r="D6" s="18">
-        <v>493856922</v>
+        <v>493631983</v>
       </c>
       <c r="E6" s="18">
-        <v>518549768</v>
+        <v>518313582</v>
       </c>
       <c r="F6" s="18">
-        <v>543242614</v>
+        <v>542995181</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -2083,19 +2083,19 @@
         <v>19</v>
       </c>
       <c r="B7" s="21">
-        <v>0.07540645544144668</v>
+        <v>0.07544081675690989</v>
       </c>
       <c r="C7" s="21">
-        <v>0.0714376946456574</v>
+        <v>0.07147024747931542</v>
       </c>
       <c r="D7" s="21">
-        <v>0.06786580992783979</v>
+        <v>0.06789673512706733</v>
       </c>
       <c r="E7" s="21">
-        <v>0.06463410470564515</v>
+        <v>0.06466355728258728</v>
       </c>
       <c r="F7" s="21">
-        <v>0.061696190866204766</v>
+        <v>0.061724304695072424</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -2103,19 +2103,19 @@
         <v>90</v>
       </c>
       <c r="B8" s="16">
-        <v>288906299.5</v>
+        <v>288774710.25000006</v>
       </c>
       <c r="C8" s="16">
-        <v>304956649.40000004</v>
+        <v>304817749.6000001</v>
       </c>
       <c r="D8" s="16">
-        <v>321006999.3</v>
+        <v>320860788.95000005</v>
       </c>
       <c r="E8" s="16">
-        <v>337057349.2</v>
+        <v>336903828.3000001</v>
       </c>
       <c r="F8" s="16">
-        <v>353107699.1</v>
+        <v>352946867.6500001</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -2123,19 +2123,19 @@
         <v>20</v>
       </c>
       <c r="B9" s="16">
-        <v>158453993.495</v>
+        <v>158381821.85249996</v>
       </c>
       <c r="C9" s="16">
-        <v>167256993.09399998</v>
+        <v>167180811.8959999</v>
       </c>
       <c r="D9" s="16">
-        <v>176059992.69299996</v>
+        <v>175979801.93949997</v>
       </c>
       <c r="E9" s="16">
-        <v>184862992.292</v>
+        <v>184778791.98299992</v>
       </c>
       <c r="F9" s="16">
-        <v>193665991.89100003</v>
+        <v>193577782.02649987</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -2143,19 +2143,19 @@
         <v>91</v>
       </c>
       <c r="B10" s="21">
-        <v>0.07540645544144668</v>
+        <v>0.07544081675690989</v>
       </c>
       <c r="C10" s="21">
-        <v>0.0714376946456574</v>
+        <v>0.07147024747931542</v>
       </c>
       <c r="D10" s="21">
-        <v>0.06786580992783979</v>
+        <v>0.06789673512706733</v>
       </c>
       <c r="E10" s="21">
-        <v>0.06463410470564515</v>
+        <v>0.06466355728258728</v>
       </c>
       <c r="F10" s="21">
-        <v>0.061696190866204766</v>
+        <v>0.061724304695072424</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -2163,19 +2163,19 @@
         <v>92</v>
       </c>
       <c r="B11" s="21">
-        <v>0.07766864910469008</v>
+        <v>0.07770404125961719</v>
       </c>
       <c r="C11" s="21">
-        <v>0.07358082548502712</v>
+        <v>0.07361435490369489</v>
       </c>
       <c r="D11" s="21">
-        <v>0.06990178422567499</v>
+        <v>0.06993363718087935</v>
       </c>
       <c r="E11" s="21">
-        <v>0.0665731278468145</v>
+        <v>0.0666034640010649</v>
       </c>
       <c r="F11" s="21">
-        <v>0.0635470765921909</v>
+        <v>0.0635760338359246</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2183,19 +2183,19 @@
         <v>93</v>
       </c>
       <c r="B12" s="21">
-        <v>0.07999870857783078</v>
+        <v>0.0800351624974057</v>
       </c>
       <c r="C12" s="21">
-        <v>0.07578825024957793</v>
+        <v>0.07582278555080572</v>
       </c>
       <c r="D12" s="21">
-        <v>0.07199883775244523</v>
+        <v>0.07203164629630572</v>
       </c>
       <c r="E12" s="21">
-        <v>0.06857032168221894</v>
+        <v>0.06860156792109684</v>
       </c>
       <c r="F12" s="21">
-        <v>0.06545348888995663</v>
+        <v>0.06548331485100232</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -2203,19 +2203,19 @@
         <v>94</v>
       </c>
       <c r="B13" s="21">
-        <v>0.08239866983516571</v>
+        <v>0.08243621737232788</v>
       </c>
       <c r="C13" s="21">
-        <v>0.07806189775706526</v>
+        <v>0.0780974691173299</v>
       </c>
       <c r="D13" s="21">
-        <v>0.07415880288501858</v>
+        <v>0.0741925956851949</v>
       </c>
       <c r="E13" s="21">
-        <v>0.07062743133268551</v>
+        <v>0.07065961495872974</v>
       </c>
       <c r="F13" s="21">
-        <v>0.06741709355665533</v>
+        <v>0.0674478142965324</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -2223,19 +2223,19 @@
         <v>95</v>
       </c>
       <c r="B14" s="21">
-        <v>0.08487062993022068</v>
+        <v>0.08490930389349771</v>
       </c>
       <c r="C14" s="21">
-        <v>0.08040375468977723</v>
+        <v>0.0804403931908498</v>
       </c>
       <c r="D14" s="21">
-        <v>0.07638356697156914</v>
+        <v>0.07641837355575073</v>
       </c>
       <c r="E14" s="21">
-        <v>0.07274625427266607</v>
+        <v>0.07277940340749164</v>
       </c>
       <c r="F14" s="21">
-        <v>0.06943960636335499</v>
+        <v>0.06947124872542837</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -2243,19 +2243,19 @@
         <v>96</v>
       </c>
       <c r="B15" s="21">
-        <v>0.06378764896586434</v>
+        <v>0.0638840341424792</v>
       </c>
       <c r="C15" s="21">
-        <v>0.052655080113720464</v>
+        <v>0.052746392410096404</v>
       </c>
       <c r="D15" s="21">
-        <v>0.04263576814228257</v>
+        <v>0.042722514844183074</v>
       </c>
       <c r="E15" s="21">
-        <v>0.03357067635492032</v>
+        <v>0.03365329227902169</v>
       </c>
       <c r="F15" s="21">
-        <v>0.02532968381792062</v>
+        <v>0.025408544487956142</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -2263,19 +2263,19 @@
         <v>97</v>
       </c>
       <c r="B16" s="21">
-        <v>0.07013321323863686</v>
+        <v>0.07023248997055016</v>
       </c>
       <c r="C16" s="21">
-        <v>0.058666667320928664</v>
+        <v>0.05876071898619588</v>
       </c>
       <c r="D16" s="21">
-        <v>0.04834677599034764</v>
+        <v>0.04843612509330515</v>
       </c>
       <c r="E16" s="21">
-        <v>0.03900973144936451</v>
+        <v>0.039094825851188925</v>
       </c>
       <c r="F16" s="21">
-        <v>0.03052150913625482</v>
+        <v>0.030602735626391413</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -2283,19 +2283,19 @@
         <v>98</v>
       </c>
       <c r="B17" s="21">
-        <v>0.07666914443959254</v>
+        <v>0.07677139947346324</v>
       </c>
       <c r="C17" s="21">
-        <v>0.0648586021443531</v>
+        <v>0.06495547535957834</v>
       </c>
       <c r="D17" s="21">
-        <v>0.05422911407385464</v>
+        <v>0.05432114364990088</v>
       </c>
       <c r="E17" s="21">
-        <v>0.04461195819664202</v>
+        <v>0.044699605430521164</v>
       </c>
       <c r="F17" s="21">
-        <v>0.03586908921413904</v>
+        <v>0.03595275249897974</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -2303,19 +2303,19 @@
         <v>99</v>
       </c>
       <c r="B18" s="21">
-        <v>0.08340115357657689</v>
+        <v>0.08350647626146374</v>
       </c>
       <c r="C18" s="21">
-        <v>0.07123629501248027</v>
+        <v>0.07133607442416227</v>
       </c>
       <c r="D18" s="21">
-        <v>0.06028792229986687</v>
+        <v>0.06038271276319449</v>
       </c>
       <c r="E18" s="21">
-        <v>0.05038225174633787</v>
+        <v>0.05047252839723339</v>
       </c>
       <c r="F18" s="21">
-        <v>0.041377096694359794</v>
+        <v>0.04146326987774572</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -2323,19 +2323,19 @@
         <v>100</v>
       </c>
       <c r="B19" s="21">
-        <v>0.09033512298767078</v>
+        <v>0.09044360535310422</v>
       </c>
       <c r="C19" s="21">
-        <v>0.07780531866665126</v>
+        <v>0.07790809146068373</v>
       </c>
       <c r="D19" s="21">
-        <v>0.06652849477265946</v>
+        <v>0.06662612894988691</v>
       </c>
       <c r="E19" s="21">
-        <v>0.05632565410252458</v>
+        <v>0.05641863905294697</v>
       </c>
       <c r="F19" s="21">
-        <v>0.04705034439898717</v>
+        <v>0.04713910277787467</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -2343,19 +2343,19 @@
         <v>101</v>
       </c>
       <c r="B20" s="21">
-        <v>0.3051600662656781</v>
+        <v>0.3057548033673661</v>
       </c>
       <c r="C20" s="21">
-        <v>0.23646743149164598</v>
+        <v>0.23703086678766805</v>
       </c>
       <c r="D20" s="21">
-        <v>0.17464406016757217</v>
+        <v>0.17517932382455192</v>
       </c>
       <c r="E20" s="21">
-        <v>0.11870862894706855</v>
+        <v>0.1192184039661173</v>
       </c>
       <c r="F20" s="21">
-        <v>0.06785823690948259</v>
+        <v>0.0683448404307912</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -2363,19 +2363,19 @@
         <v>102</v>
       </c>
       <c r="B21" s="21">
-        <v>0.19776225955946908</v>
+        <v>0.19804399800640082</v>
       </c>
       <c r="C21" s="21">
-        <v>0.16480600824498656</v>
+        <v>0.16507976492239737</v>
       </c>
       <c r="D21" s="21">
-        <v>0.13440340622976676</v>
+        <v>0.13466981078712764</v>
       </c>
       <c r="E21" s="21">
-        <v>0.1062419826976042</v>
+        <v>0.10650158669829789</v>
       </c>
       <c r="F21" s="21">
-        <v>0.08006020158009884</v>
+        <v>0.08031349136960966</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -2383,19 +2383,19 @@
         <v>103</v>
       </c>
       <c r="B22" s="21">
-        <v>0.1640312040692767</v>
+        <v>0.16421973287714633</v>
       </c>
       <c r="C22" s="21">
-        <v>0.14189339102563064</v>
+        <v>0.14207798455287163</v>
       </c>
       <c r="D22" s="21">
-        <v>0.12131773121437824</v>
+        <v>0.12149868324346302</v>
       </c>
       <c r="E22" s="21">
-        <v>0.10212220557189852</v>
+        <v>0.10229977417512098</v>
       </c>
       <c r="F22" s="21">
-        <v>0.08415355380487459</v>
+        <v>0.08432796718472907</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -2403,19 +2403,19 @@
         <v>104</v>
       </c>
       <c r="B23" s="21">
-        <v>0.14756246534505224</v>
+        <v>0.1477064209085694</v>
       </c>
       <c r="C23" s="21">
-        <v>0.1306312346467733</v>
+        <v>0.13077264129698024</v>
       </c>
       <c r="D23" s="21">
-        <v>0.11484476767048893</v>
+        <v>0.11498381664943533</v>
       </c>
       <c r="E23" s="21">
-        <v>0.10007211514126554</v>
+        <v>0.10020897408796034</v>
       </c>
       <c r="F23" s="21">
-        <v>0.08620281882844336</v>
+        <v>0.08633763570082348</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -2423,19 +2423,19 @@
         <v>105</v>
       </c>
       <c r="B24" s="21">
-        <v>0.13782197891223996</v>
+        <v>0.13793987380682698</v>
       </c>
       <c r="C24" s="21">
-        <v>0.12394569453066966</v>
+        <v>0.12406167178563905</v>
       </c>
       <c r="D24" s="21">
-        <v>0.11098881744447722</v>
+        <v>0.11110302503306577</v>
       </c>
       <c r="E24" s="21">
-        <v>0.09884676831523623</v>
+        <v>0.0989593354686445</v>
       </c>
       <c r="F24" s="21">
-        <v>0.08743131836532285</v>
+        <v>0.08754235875933113</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2443,19 +2443,19 @@
         <v>106</v>
       </c>
       <c r="B25" s="21">
-        <v>0.7201291802973258</v>
+        <v>0.7217974470626427</v>
       </c>
       <c r="C25" s="21">
-        <v>0.5274429677477039</v>
+        <v>0.5290234314113507</v>
       </c>
       <c r="D25" s="21">
-        <v>0.3540253763755715</v>
+        <v>0.3555268172078867</v>
       </c>
       <c r="E25" s="21">
-        <v>0.1971237460224773</v>
+        <v>0.19855368997595596</v>
       </c>
       <c r="F25" s="21">
-        <v>0.0544859001946362</v>
+        <v>0.05585084695881587</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -2463,19 +2463,19 @@
         <v>107</v>
       </c>
       <c r="B26" s="21">
-        <v>0.3968478252463211</v>
+        <v>0.39752643998053394</v>
       </c>
       <c r="C26" s="21">
-        <v>0.316408338517372</v>
+        <v>0.3170856935937435</v>
       </c>
       <c r="D26" s="21">
-        <v>0.2401080983493426</v>
+        <v>0.24078650000694493</v>
       </c>
       <c r="E26" s="21">
-        <v>0.1672931111833925</v>
+        <v>0.1679749281038763</v>
       </c>
       <c r="F26" s="21">
-        <v>0.09739049591255954</v>
+        <v>0.09807823568436566</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -2483,19 +2483,19 @@
         <v>108</v>
       </c>
       <c r="B27" s="21">
-        <v>0.302364335943337</v>
+        <v>0.30278931982615276</v>
       </c>
       <c r="C27" s="21">
-        <v>0.2516737597947342</v>
+        <v>0.25210327828454404</v>
       </c>
       <c r="D27" s="21">
-        <v>0.2029877503961316</v>
+        <v>0.203423332414298</v>
       </c>
       <c r="E27" s="21">
-        <v>0.1559416083787586</v>
+        <v>0.1563848863963111</v>
       </c>
       <c r="F27" s="21">
-        <v>0.11020839383369198</v>
+        <v>0.11066115572491395</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -2503,19 +2503,19 @@
         <v>109</v>
       </c>
       <c r="B28" s="21">
-        <v>0.2569845262749542</v>
+        <v>0.2572956894912961</v>
       </c>
       <c r="C28" s="21">
-        <v>0.21981464387715918</v>
+        <v>0.22013006280158073</v>
       </c>
       <c r="D28" s="21">
-        <v>0.18400970543377648</v>
+        <v>0.18433050254637917</v>
       </c>
       <c r="E28" s="21">
-        <v>0.1493126658608035</v>
+        <v>0.1496400339417382</v>
       </c>
       <c r="F28" s="21">
-        <v>0.11549344795867181</v>
+        <v>0.11582868483174119</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -2523,19 +2523,19 @@
         <v>110</v>
       </c>
       <c r="B29" s="21">
-        <v>0.23013228950586842</v>
+        <v>0.23037947493767016</v>
       </c>
       <c r="C29" s="21">
-        <v>0.2006130298309211</v>
+        <v>0.20086345557656937</v>
       </c>
       <c r="D29" s="21">
-        <v>0.17219459290171063</v>
+        <v>0.17244912782092867</v>
       </c>
       <c r="E29" s="21">
-        <v>0.14467454984822398</v>
+        <v>0.14493410085578995</v>
       </c>
       <c r="F29" s="21">
-        <v>0.11787362332726423</v>
+        <v>0.11813915964912869</v>
       </c>
     </row>
   </sheetData>
